--- a/CHATGPT/Kalkulation_preise/Kalkulation und Rezepte.xlsx
+++ b/CHATGPT/Kalkulation_preise/Kalkulation und Rezepte.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Geschäft und Privat\Kamin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Geschäft und Privat\Kamin\Rezepte\Kakulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="129">
   <si>
     <t>netto</t>
   </si>
@@ -303,9 +303,6 @@
     <t>Pola-Pola</t>
   </si>
   <si>
-    <t>Rinderleber</t>
-  </si>
-  <si>
     <t>Cobanska Pljeskavica</t>
   </si>
   <si>
@@ -339,9 +336,6 @@
     <t>Kaukasischer Teller</t>
   </si>
   <si>
-    <t>Sauerfleisch 260</t>
-  </si>
-  <si>
     <t>Wieder Schnitzel</t>
   </si>
   <si>
@@ -408,13 +402,7 @@
     <t>Steak-Platte</t>
   </si>
   <si>
-    <t>Sauerfleisch 130</t>
-  </si>
-  <si>
     <t>Currywurst</t>
-  </si>
-  <si>
-    <t>kleine Rinderleber</t>
   </si>
   <si>
     <t>Preis</t>
@@ -473,6 +461,9 @@
   </si>
   <si>
     <t>Verlust in gram</t>
+  </si>
+  <si>
+    <t>Dubrovnik Teller</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1050,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
         <v>46</v>
@@ -1532,7 +1523,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
@@ -1543,7 +1534,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B57" t="s">
         <v>46</v>
@@ -1554,7 +1545,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
         <v>46</v>
@@ -1571,7 +1562,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="3">
-        <v>1.1499999999999999</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1593,7 +1584,7 @@
         <v>46</v>
       </c>
       <c r="C61" s="3">
-        <v>1.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1615,7 +1606,7 @@
         <v>46</v>
       </c>
       <c r="C63" s="3">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1642,7 +1633,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
         <v>46</v>
@@ -1653,10 +1644,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C67" s="3">
         <v>2.4500000000000002</v>
@@ -1664,10 +1655,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B68" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C68" s="3">
         <v>2.89</v>
@@ -1684,7 +1675,7 @@
         <v>46</v>
       </c>
       <c r="C70" s="3">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1695,7 +1686,7 @@
         <v>46</v>
       </c>
       <c r="C71" s="3">
-        <v>6.25</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -1703,7 +1694,7 @@
         <v>58</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C72" s="3">
         <v>1.29</v>
@@ -1750,10 +1741,10 @@
         <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1864,7 +1855,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B13" s="7">
         <v>1000</v>
@@ -1981,7 +1972,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B25" s="7">
         <v>200</v>
@@ -1992,7 +1983,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B26" s="7">
         <v>280</v>
@@ -2007,7 +1998,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B28" s="7">
         <v>370</v>
@@ -2489,10 +2480,10 @@
         <v>73</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2500,10 +2491,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="13">
-        <v>17.600000000000001</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2514,7 +2505,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="13">
-        <v>13.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2525,7 +2516,7 @@
         <v>76</v>
       </c>
       <c r="C4" s="13">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2536,29 +2527,24 @@
         <v>77</v>
       </c>
       <c r="C5" s="13">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="13">
-        <v>11.9</v>
-      </c>
+      <c r="C6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="13">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2566,10 +2552,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="13">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2577,10 +2563,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="13">
-        <v>15.9</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2591,7 +2577,7 @@
         <v>74</v>
       </c>
       <c r="C10" s="13">
-        <v>17.899999999999999</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2599,10 +2585,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="13">
-        <v>16.899999999999999</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2610,10 +2596,10 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="13">
-        <v>14.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2621,10 +2607,10 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="13">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2632,10 +2618,10 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="13">
-        <v>31.4</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2643,10 +2629,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="13">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2654,10 +2640,10 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="13">
-        <v>38.200000000000003</v>
+        <v>39.200000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2665,32 +2651,27 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" s="13">
-        <v>17.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>22</v>
       </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="13">
-        <v>14.1</v>
-      </c>
+      <c r="C18" s="13"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" s="13">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2698,10 +2679,10 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C20" s="13">
-        <v>14.2</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2709,7 +2690,7 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" s="13">
         <v>9.1999999999999993</v>
@@ -2720,10 +2701,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C22" s="13">
-        <v>16.899999999999999</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2731,10 +2712,10 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C23" s="13">
-        <v>15.8</v>
+        <v>16.899999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2742,7 +2723,7 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" s="13">
         <v>8.6999999999999993</v>
@@ -2753,7 +2734,7 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C25" s="13">
         <v>8.5</v>
@@ -2764,10 +2745,10 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C26" s="13">
-        <v>17.7</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2775,10 +2756,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C27" s="13">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2786,7 +2767,7 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C28" s="13">
         <v>9.8000000000000007</v>
@@ -2797,10 +2778,10 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C29" s="13">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2808,10 +2789,10 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C30" s="13">
-        <v>23.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2819,10 +2800,10 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C31" s="13">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2830,10 +2811,10 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C32" s="13">
-        <v>22.5</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2841,10 +2822,10 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C33" s="13">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2852,10 +2833,10 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C34" s="13">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2863,10 +2844,10 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C35" s="13">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2874,10 +2855,10 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C36" s="13">
-        <v>25.4</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2885,10 +2866,10 @@
         <v>418</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C37" s="13">
-        <v>23.7</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2896,10 +2877,10 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C38" s="13">
-        <v>26.6</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2907,10 +2888,10 @@
         <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C39" s="13">
-        <v>17.899999999999999</v>
+        <v>19.100000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2921,7 +2902,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="13">
-        <v>16.899999999999999</v>
+        <v>18.100000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2929,10 +2910,10 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C41" s="13">
-        <v>16.899999999999999</v>
+        <v>18.100000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2940,10 +2921,10 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C42" s="13">
-        <v>58.2</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2951,10 +2932,10 @@
         <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C43" s="13">
-        <v>8.4</v>
+        <v>17.899999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2962,7 +2943,7 @@
         <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C44" s="13">
         <v>7.1</v>
@@ -2972,19 +2953,14 @@
       <c r="A45">
         <v>96</v>
       </c>
-      <c r="B45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="13">
-        <v>8.9</v>
-      </c>
+      <c r="C45" s="13"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C46" s="13">
         <v>8.9</v>
